--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339513</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,121 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129922692</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästviken, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>415325</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6575432</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>S-Ham-0062</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129922692</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129922692</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129922692</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129922692</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129922692</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129922692</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339513</v>
+        <v>129339482</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415327</v>
+        <v>415403</v>
       </c>
       <c r="R2" t="n">
-        <v>6575438</v>
+        <v>6575511</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +797,7 @@
         <v>129339498</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129339503</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129922692</v>
+        <v>129339513</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,27 +1062,30 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästviken, SO om, Vrm</t>
+          <t>Hästviken, Hästviken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415325</v>
+        <v>415327</v>
       </c>
       <c r="R5" t="n">
-        <v>6575432</v>
+        <v>6575438</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,19 +1107,24 @@
           <t>Hammarö</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>S-Ham-0062</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1139,246 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129922691</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästviken, OSO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>415402</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6575511</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S-Ham-0063</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Även en dellokal ca 15 m åt SV med 8 skott.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Åsa Duell</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129922692</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästviken, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>415325</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6575432</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>S-Ham-0062</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 58382-2024 artfynd.xlsx
+++ b/artfynd/A 58382-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339513</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129922691</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,8 +1413,21 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129922692</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>